--- a/outputs/submission_tables_xlsx/Supplementary Table 8.xlsx
+++ b/outputs/submission_tables_xlsx/Supplementary Table 8.xlsx
@@ -7,7 +7,8 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="A - Drift basis" sheetId="1" r:id="rId1"/>
+    <sheet name="B - Impact in 2050" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -343,169 +344,183 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Income group</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Model role</t>
+          <t>Effective VSLY in 1990</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Forecast-actual pairs</t>
+          <t>Effective VSLY in 2023</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MAPE (%)</t>
+          <t>Endpoint CAGR (%/year, published basis)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>MASE</t>
+          <t>Log-linear OLS CAGR (%/year, bounding check)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Mean ratio of absolute error to the naive benchmark</t>
+          <t>Log-linear R squared</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Empirical coverage of the nominal 95% range (%)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Series with the lowest MAPE among the four candidates</t>
+          <t>Difference (percentage points per year)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARIMA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Candidate</t>
-        </is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>13513.84832241552</v>
       </c>
       <c r="C2">
-        <v>552</v>
+        <v>13652.93797022442</v>
       </c>
       <c r="D2">
-        <v>4.180488721618111</v>
+        <v>0.03103443000165296</v>
       </c>
       <c r="E2">
-        <v>2.368489364366633</v>
+        <v>0.01957712549367496</v>
       </c>
       <c r="F2">
-        <v>0.4173386677461484</v>
+        <v>0.1316077380194902</v>
       </c>
       <c r="G2">
-        <v>55.07246376811595</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
+        <v>-0.01145730450797799</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Candidate</t>
-        </is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>57351.02733142021</v>
       </c>
       <c r="C3">
-        <v>552</v>
+        <v>60365.1625571617</v>
       </c>
       <c r="D3">
-        <v>4.916615734160605</v>
+        <v>0.1553368954030798</v>
       </c>
       <c r="E3">
-        <v>2.78853262469526</v>
+        <v>0.1715897613505657</v>
       </c>
       <c r="F3">
-        <v>0.5505105873803431</v>
+        <v>0.7870660069175858</v>
       </c>
       <c r="G3">
-        <v>55.43478260869566</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>0.01625286594748587</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Candidate</t>
-        </is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>142924.1507636413</v>
       </c>
       <c r="C4">
-        <v>552</v>
+        <v>140261.0422245954</v>
       </c>
       <c r="D4">
-        <v>7.071429618336656</v>
+        <v>-0.05698012851151901</v>
       </c>
       <c r="E4">
-        <v>3.943318263018461</v>
+        <v>-0.07747190461725451</v>
       </c>
       <c r="F4">
-        <v>0.6220484825066162</v>
+        <v>0.8224230630783551</v>
       </c>
       <c r="G4">
-        <v>26.26811594202898</v>
-      </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Naive</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Candidate</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>552</v>
-      </c>
-      <c r="D5">
-        <v>12.67866550752783</v>
-      </c>
-      <c r="E5">
-        <v>7.000532938084895</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>22.82608695652174</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>-0.02049177610573549</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed-composition VLW in 2050 (billion constant-2023 USD)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Drift-adjusted VLW in 2050 (billion constant-2023 USD)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Difference (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Endpoint CAGR, 1990 and 2023 only (published basis)</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1195.059287771596</v>
+      </c>
+      <c r="C2">
+        <v>1189.195770368219</v>
+      </c>
+      <c r="D2">
+        <v>-0.4906465698711338</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Log-linear OLS on all 34 annual observations (bounding check)</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1195.059287771596</v>
+      </c>
+      <c r="C3">
+        <v>1184.824913221494</v>
+      </c>
+      <c r="D3">
+        <v>-0.8563905284720952</v>
       </c>
     </row>
   </sheetData>
